--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488076_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488076_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.015700000000001</v>
+        <v>7.029</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1878</v>
+        <v>4.6785</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8279</v>
+        <v>2.3505</v>
       </c>
       <c r="G2" t="n">
         <v>4.0547</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1411</v>
+        <v>1.1544</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6227</v>
+        <v>1.1133</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5184</v>
+        <v>0.0411</v>
       </c>
       <c r="V2" t="n">
         <v>1.4234</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0221</v>
+        <v>5.331</v>
       </c>
       <c r="E3" t="n">
         <v>7.1918</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1697</v>
+        <v>-1.8608</v>
       </c>
       <c r="G3" t="n">
         <v>5.0488</v>
@@ -688,13 +688,13 @@
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6897</v>
+        <v>-0.3808</v>
       </c>
       <c r="T3" t="n">
         <v>-0.0476</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6421</v>
+        <v>-0.3333</v>
       </c>
       <c r="V3" t="n">
         <v>0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5795</v>
+        <v>0.4427</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6337</v>
+        <v>1.7605</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0542</v>
+        <v>-1.3178</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1241</v>
+        <v>1.5415</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6107</v>
+        <v>0.2903</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4866</v>
+        <v>1.2512</v>
       </c>
       <c r="J4" t="n">
-        <v>2.325</v>
+        <v>2.056</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2139</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2.539</v>
+        <v>1.3699</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4491</v>
+        <v>-0.5144</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3967</v>
+        <v>-0.3957</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0524</v>
+        <v>-0.1187</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>5.0909</v>
+        <v>-0.8829</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3613</v>
+        <v>-0.2954</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7296</v>
+        <v>-0.5874</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5944</v>
+        <v>-1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.524</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3513</v>
+        <v>0.3446</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5568</v>
+        <v>2.4549</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2055</v>
+        <v>-2.1103</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5415</v>
+        <v>-0.1241</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2903</v>
+        <v>-1.6107</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2512</v>
+        <v>1.4866</v>
       </c>
       <c r="J5" t="n">
-        <v>2.056</v>
+        <v>2.325</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6860000000000001</v>
+        <v>-0.2139</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3699</v>
+        <v>2.539</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5144</v>
+        <v>-2.4491</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3957</v>
+        <v>-1.3967</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1187</v>
+        <v>-1.0524</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9743000000000001</v>
+        <v>2.856</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4992</v>
+        <v>2.1825</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4751</v>
+        <v>0.6734</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2071</v>
+        <v>-1.5944</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2071</v>
+        <v>-1.524</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.059</v>
+        <v>0.1823</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5172</v>
+        <v>1.4777</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5762</v>
+        <v>-1.2954</v>
       </c>
       <c r="G6" t="n">
         <v>-1.9681</v>
@@ -922,13 +922,13 @@
         <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4368</v>
+        <v>-0.1955</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1834</v>
+        <v>-0.2229</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2534</v>
+        <v>0.0274</v>
       </c>
       <c r="V6" t="n">
         <v>2.1476</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1631</v>
+        <v>0.1505</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7476</v>
+        <v>1.1455</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9107</v>
+        <v>-0.9949</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9997</v>
+        <v>-0.8685</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9626</v>
+        <v>-0.2545</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0371</v>
+        <v>-0.6141</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1967</v>
+        <v>-0.5637</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9155</v>
+        <v>0.0674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2812</v>
+        <v>-0.6312</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.1964</v>
+        <v>-0.3048</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.878</v>
+        <v>-0.3219</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3184</v>
+        <v>0.0171</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7771</v>
+        <v>-0.0496</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0772</v>
+        <v>0.5021</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6998</v>
+        <v>-0.5517</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2666</v>
+        <v>-0.1207</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2455</v>
+        <v>-0.2174</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0624</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1831</v>
+        <v>-0.155</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2018</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0437</v>
+        <v>-0.0156</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9067</v>
+        <v>-0.4658</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2287</v>
+        <v>2.81</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1353</v>
+        <v>-3.2758</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8685</v>
+        <v>-1.9997</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2545</v>
+        <v>-0.9626</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6141</v>
+        <v>-1.0371</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5637</v>
+        <v>1.1967</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0674</v>
+        <v>0.9155</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6312</v>
+        <v>0.2812</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3048</v>
+        <v>-3.1964</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3219</v>
+        <v>-1.878</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0171</v>
+        <v>-1.3184</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1068</v>
+        <v>0.4744</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4147</v>
+        <v>0.1396</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6921</v>
+        <v>0.3348</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1207</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3278</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1602</v>
+        <v>-0.6694</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3793</v>
+        <v>0.6454</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5395</v>
+        <v>-1.3149</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1086</v>
@@ -1234,13 +1234,13 @@
         <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0602</v>
+        <v>1.551</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1528</v>
+        <v>1.4189</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0926</v>
+        <v>0.132</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1207</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.348</v>
+        <v>-0.7295</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6867</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6613</v>
+        <v>-0.6332</v>
       </c>
       <c r="G11" t="n">
         <v>0.6149</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8073</v>
+        <v>0.8113</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5909</v>
+        <v>0.9996</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2164</v>
+        <v>-0.1883</v>
       </c>
       <c r="V11" t="n">
         <v>1.016</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0861</v>
+        <v>11.398</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6938</v>
+        <v>22.0057</v>
       </c>
       <c r="F12" t="n">
         <v>-10.6076</v>
@@ -1375,7 +1375,7 @@
         <v>-14.8179</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.641399999999999</v>
+        <v>-9.641400000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-5.176600000000001</v>
@@ -1390,13 +1390,13 @@
         <v>10.9022</v>
       </c>
       <c r="S12" t="n">
-        <v>5.0107</v>
+        <v>5.322699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.415799999999999</v>
+        <v>5.7277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4052000000000001</v>
+        <v>-0.4052</v>
       </c>
       <c r="V12" t="n">
         <v>2.0773</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6197</v>
+        <v>3.4913</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1812</v>
+        <v>5.3663</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5615</v>
+        <v>-1.8749</v>
       </c>
       <c r="G13" t="n">
         <v>1.332</v>
@@ -1468,13 +1468,13 @@
         <v>1.5858</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0571</v>
+        <v>0.9287</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3327</v>
+        <v>0.5178</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7244</v>
+        <v>0.4109</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1569</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0005</v>
+        <v>1.1369</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5656</v>
+        <v>3.6699</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5651</v>
+        <v>-2.533</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3465</v>
+        <v>3.0312</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1363</v>
+        <v>-0.2289</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2102</v>
+        <v>3.2601</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8313</v>
+        <v>6.0219</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6786</v>
+        <v>1.036</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5099</v>
+        <v>4.9859</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1779</v>
+        <v>-2.9907</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4577</v>
+        <v>-1.2648</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7201</v>
+        <v>-1.7258</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.5769</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1716</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5138</v>
+        <v>-1.2022</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8922</v>
+        <v>-0.3697</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6216</v>
+        <v>-0.8325</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4101</v>
+        <v>-0.4939</v>
       </c>
       <c r="W14" t="n">
-        <v>4.0137</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>-0.4939</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0914</v>
+        <v>0.2847</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3643</v>
+        <v>0.8253</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2729</v>
+        <v>-0.5406</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0312</v>
+        <v>1.0277</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2289</v>
+        <v>2.4129</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2601</v>
+        <v>-1.3852</v>
       </c>
       <c r="J15" t="n">
-        <v>6.0219</v>
+        <v>1.3988</v>
       </c>
       <c r="K15" t="n">
-        <v>1.036</v>
+        <v>1.9976</v>
       </c>
       <c r="L15" t="n">
-        <v>4.9859</v>
+        <v>-0.5988</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9907</v>
+        <v>-0.3711</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2648</v>
+        <v>0.4153</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7258</v>
+        <v>-0.7864</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2476</v>
+        <v>-0.8801</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6753</v>
+        <v>-0.5735</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.5723</v>
+        <v>-0.3066</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4939</v>
+        <v>-1.0522</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4939</v>
+        <v>-1.0522</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0561</v>
+        <v>0.1905</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7235</v>
+        <v>2.1581</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6673</v>
+        <v>-1.9676</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0277</v>
+        <v>-1.3465</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4129</v>
+        <v>-1.1363</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3852</v>
+        <v>-0.2102</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3988</v>
+        <v>0.8313</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9976</v>
+        <v>-0.6786</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5988</v>
+        <v>1.5099</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3711</v>
+        <v>-2.1779</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4153</v>
+        <v>-0.4577</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7864</v>
+        <v>-1.7201</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1893</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1087</v>
+        <v>0.7039</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6753</v>
+        <v>0.4847</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4333</v>
+        <v>0.2192</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0522</v>
+        <v>3.4101</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.0137</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0522</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8559</v>
+        <v>-0.6757</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5351</v>
+        <v>0.3314</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.391</v>
+        <v>-1.0071</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2862</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5088</v>
+        <v>-0.3285</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3671</v>
+        <v>0.1634</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8759</v>
+        <v>-0.4919</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4485</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4332</v>
+        <v>-1.0997</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0853</v>
+        <v>0.424</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3479</v>
+        <v>-1.5238</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3343</v>
@@ -1858,13 +1858,13 @@
         <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.0557</v>
+        <v>-0.7222</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5395</v>
+        <v>-0.0302</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.5161</v>
+        <v>-0.6921</v>
       </c>
       <c r="V18" t="n">
         <v>0.9657</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4552</v>
+        <v>-2.2294</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7204</v>
+        <v>0.7683</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7349</v>
+        <v>-2.9976</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6515</v>
+        <v>-1.5328</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0551</v>
+        <v>0.652</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7066</v>
+        <v>-2.1849</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1414</v>
+        <v>0.4411</v>
       </c>
       <c r="K19" t="n">
-        <v>0.377</v>
+        <v>1.036</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5184</v>
+        <v>-0.5949</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5101</v>
+        <v>-1.9739</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3219</v>
+        <v>-0.3839</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1882</v>
+        <v>-1.59</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.5947</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.1805</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1747</v>
+        <v>-0.1019</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0683</v>
+        <v>0.1112</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.243</v>
+        <v>-0.213</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3621</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.171</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5115</v>
+        <v>-2.7843</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8701</v>
+        <v>-1.4335</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3816</v>
+        <v>-1.3509</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5328</v>
+        <v>-1.6515</v>
       </c>
       <c r="H20" t="n">
-        <v>0.652</v>
+        <v>0.0551</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1849</v>
+        <v>-1.7066</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4411</v>
+        <v>-0.1414</v>
       </c>
       <c r="K20" t="n">
-        <v>1.036</v>
+        <v>0.377</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5949</v>
+        <v>-0.5184</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9739</v>
+        <v>-1.5101</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3839</v>
+        <v>-0.3219</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.59</v>
+        <v>-1.1882</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-2.1805</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.384</v>
+        <v>-0.5038</v>
       </c>
       <c r="T20" t="n">
-        <v>0.213</v>
+        <v>0.3553</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.597</v>
+        <v>-0.8591</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3621</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2071</v>
+        <v>0.5331</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>-0.171</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.7683</v>
+        <v>-5.8854</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2843</v>
+        <v>-1.6731</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.484</v>
+        <v>-4.2124</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4938</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8515</v>
+        <v>-0.2403</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0476</v>
+        <v>0.3192</v>
       </c>
       <c r="V21" t="n">
         <v>-3.6776</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.256399999999999</v>
+        <v>-7.571099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>11.1498</v>
+        <v>10.4367</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.4062</v>
+        <v>-18.0079</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2542</v>
+        <v>-3.254200000000001</v>
       </c>
       <c r="H22" t="n">
         <v>3.8952</v>
@@ -2170,13 +2170,13 @@
         <v>10.5057</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.7125</v>
+        <v>-2.0272</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1317</v>
+        <v>0.4187</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.844</v>
+        <v>-2.4459</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0912</v>
@@ -2185,7 +2185,7 @@
         <v>6.287</v>
       </c>
       <c r="X22" t="n">
-        <v>-8.378299999999999</v>
+        <v>-8.378300000000001</v>
       </c>
     </row>
   </sheetData>
